--- a/1_Data_Master/Data Absensi_BMP.xlsx
+++ b/1_Data_Master/Data Absensi_BMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GENERAL PSD\PENDINGAN LINDAA 2026\GENERAL 2026\00. PORTAL TIMESHEET\1_Data_Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF838B9-207E-4D92-8D62-816F7A41E125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C81FC8-3603-4A84-869A-EF8AD25A25C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CEF79333-F3A4-451D-BE26-4BA9C1711C1C}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="115">
   <si>
     <t>D</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>NOVITA FITRI</t>
-  </si>
-  <si>
-    <t>Fuelman - Mining</t>
   </si>
   <si>
     <t>FUELMAN</t>
@@ -174,9 +171,6 @@
     <t>AHMAD NOR</t>
   </si>
   <si>
-    <t>Oilman - Mining</t>
-  </si>
-  <si>
     <t>INPUT DAN POSTING FOG</t>
   </si>
   <si>
@@ -187,9 +181,6 @@
   </si>
   <si>
     <t>NANDA RIZKY BUDIANTO</t>
-  </si>
-  <si>
-    <t>Field Support - Warehouse Mining</t>
   </si>
   <si>
     <t>GR GI DAN SUPPLY BARANG</t>
@@ -216,9 +207,6 @@
     <t>DENIS DAMARA</t>
   </si>
   <si>
-    <t>Admin Inventory - Mining</t>
-  </si>
-  <si>
     <t>STOCK TAKER</t>
   </si>
   <si>
@@ -228,16 +216,10 @@
     <t>BUDIMAN</t>
   </si>
   <si>
-    <t>Admin Support - Purchasing Mining</t>
-  </si>
-  <si>
     <t>PENGADAAN DAN GENERAL PR TO PO</t>
   </si>
   <si>
     <t>DAFRIT TIERO BERNANDO</t>
-  </si>
-  <si>
-    <t>Fuelman - Hauling</t>
   </si>
   <si>
     <t>HAJU</t>
@@ -276,22 +258,13 @@
     <t>AHMAD KURNIAWAN</t>
   </si>
   <si>
-    <t>Admin Support - FOG Hauling</t>
-  </si>
-  <si>
     <t>SERBIANTO</t>
   </si>
   <si>
     <t>DWIKY RYAMIZARDIN</t>
   </si>
   <si>
-    <t>Oilman - Hauling</t>
-  </si>
-  <si>
     <t>SYARIFUDIN</t>
-  </si>
-  <si>
-    <t>Field Support - Warehouse Hauling</t>
   </si>
   <si>
     <t>NOVARI FADLI</t>
@@ -397,6 +370,24 @@
   </si>
   <si>
     <t>Refueling Resttime Jum'at</t>
+  </si>
+  <si>
+    <t>FOG Hauling</t>
+  </si>
+  <si>
+    <t>Purchasing Mining</t>
+  </si>
+  <si>
+    <t>Inventory Mining</t>
+  </si>
+  <si>
+    <t>Warehouse Mining</t>
+  </si>
+  <si>
+    <t>Warehouse Hauling</t>
+  </si>
+  <si>
+    <t>FOG Mining</t>
   </si>
 </sst>
 </file>
@@ -3078,29 +3069,29 @@
         <v>11</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H2" s="5">
         <f>IFERROR(MOD(14-(MATCH("OFF",I2:AL2,0)-1)-1,14)+1,"1")</f>
         <v>2</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>0</v>
@@ -3118,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R2" s="6" t="s">
         <v>0</v>
@@ -3130,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V2" s="6" t="s">
         <v>0</v>
@@ -3172,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ2" s="6" t="s">
         <v>0</v>
@@ -3186,7 +3177,7 @@
       <c r="AM2" s="8"/>
       <c r="AN2" s="9"/>
       <c r="AO2" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP2" s="10" t="str">
         <f>AO2&amp;"D"</f>
@@ -3205,19 +3196,19 @@
         <v>207231</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" s="5">
         <f t="shared" ref="H3:H50" si="1">IFERROR(MOD(14-(MATCH("OFF",I3:AL3,0)-1)-1,14)+1,"1")</f>
@@ -3236,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>0</v>
@@ -3272,50 +3263,50 @@
         <v>0</v>
       </c>
       <c r="Y3" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM3" s="8"/>
       <c r="AO3" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP3" s="10" t="str">
         <f t="shared" ref="AP3:AP6" si="2">AO3&amp;"D"</f>
@@ -3333,19 +3324,19 @@
         <v>200509255</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" s="5">
         <f t="shared" si="1"/>
@@ -3367,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O4" s="6" t="s">
         <v>0</v>
@@ -3427,24 +3418,24 @@
         <v>0</v>
       </c>
       <c r="AH4" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI4" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ4" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK4" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL4" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM4" s="8"/>
       <c r="AN4" s="9"/>
       <c r="AO4" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP4" s="10" t="str">
         <f t="shared" si="2"/>
@@ -3462,19 +3453,19 @@
         <v>603222</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" s="5">
         <f t="shared" si="1"/>
@@ -3487,22 +3478,22 @@
         <v>0</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q5" s="6" t="s">
         <v>0</v>
@@ -3529,22 +3520,22 @@
         <v>0</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z5" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA5" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB5" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC5" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD5" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE5" s="6" t="s">
         <v>0</v>
@@ -3572,7 +3563,7 @@
       </c>
       <c r="AM5" s="8"/>
       <c r="AO5" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP5" s="10" t="str">
         <f t="shared" si="2"/>
@@ -3590,44 +3581,44 @@
         <v>1906253</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P6" s="6" t="s">
         <v>0</v>
@@ -3636,19 +3627,19 @@
         <v>0</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S6" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U6" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V6" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W6" s="6" t="s">
         <v>0</v>
@@ -3678,19 +3669,19 @@
         <v>0</v>
       </c>
       <c r="AF6" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG6" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH6" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI6" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ6" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK6" s="6" t="s">
         <v>0</v>
@@ -3700,7 +3691,7 @@
       </c>
       <c r="AM6" s="8"/>
       <c r="AO6" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP6" s="10" t="str">
         <f t="shared" si="2"/>
@@ -3718,19 +3709,19 @@
         <v>1705261</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" s="5">
         <f t="shared" si="1"/>
@@ -3749,22 +3740,22 @@
         <v>0</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>0</v>
@@ -3791,22 +3782,22 @@
         <v>0</v>
       </c>
       <c r="AA7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG7" s="6" t="s">
         <v>0</v>
@@ -3833,19 +3824,19 @@
         <v>2103223</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" s="5" t="str">
         <f t="shared" si="1"/>
@@ -3864,55 +3855,55 @@
         <v>0</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD8" s="6" t="s">
         <v>0</v>
@@ -3927,23 +3918,23 @@
         <v>0</v>
       </c>
       <c r="AH8" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI8" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ8" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK8" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL8" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM8" s="8"/>
       <c r="AO8" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP8" s="10" t="str">
         <f>AO8&amp;"N"</f>
@@ -3957,38 +3948,38 @@
         <v>1611241</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N9" s="6" t="s">
         <v>0</v>
@@ -4015,22 +4006,22 @@
         <v>0</v>
       </c>
       <c r="V9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA9" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB9" s="6" t="s">
         <v>0</v>
@@ -4057,17 +4048,17 @@
         <v>0</v>
       </c>
       <c r="AJ9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM9" s="8"/>
       <c r="AO9" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP9" s="10" t="str">
         <f t="shared" ref="AP9:AP13" si="3">AO9&amp;"N"</f>
@@ -4081,32 +4072,32 @@
         <v>2006251</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" s="5">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>0</v>
@@ -4133,22 +4124,22 @@
         <v>0</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y10" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z10" s="6" t="s">
         <v>0</v>
@@ -4157,41 +4148,41 @@
         <v>0</v>
       </c>
       <c r="AB10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM10" s="8"/>
       <c r="AO10" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AP10" s="10" t="str">
         <f t="shared" si="3"/>
@@ -4209,32 +4200,32 @@
         <v>1912241</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H11" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>0</v>
@@ -4249,28 +4240,28 @@
         <v>0</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W11" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X11" s="6" t="s">
         <v>0</v>
@@ -4291,35 +4282,35 @@
         <v>0</v>
       </c>
       <c r="AD11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK11" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL11" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM11" s="8"/>
       <c r="AO11" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP11" s="10" t="str">
         <f t="shared" si="3"/>
@@ -4337,19 +4328,19 @@
         <v>1004255</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H12" s="5">
         <f t="shared" si="1"/>
@@ -4374,28 +4365,28 @@
         <v>0</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W12" s="6" t="s">
         <v>0</v>
@@ -4416,28 +4407,28 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ12" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK12" s="6" t="s">
         <v>0</v>
@@ -4447,7 +4438,7 @@
       </c>
       <c r="AM12" s="8"/>
       <c r="AO12" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP12" s="10" t="str">
         <f t="shared" si="3"/>
@@ -4466,44 +4457,44 @@
         <v>1004254</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H13" s="5">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>0</v>
@@ -4524,28 +4515,28 @@
         <v>0</v>
       </c>
       <c r="V13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC13" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD13" s="6" t="s">
         <v>0</v>
@@ -4566,17 +4557,17 @@
         <v>0</v>
       </c>
       <c r="AJ13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM13" s="8"/>
       <c r="AO13" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP13" s="10" t="str">
         <f t="shared" si="3"/>
@@ -4594,47 +4585,47 @@
         <v>2604251</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>0</v>
@@ -4658,49 +4649,49 @@
         <v>0</v>
       </c>
       <c r="X14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM14" s="8"/>
     </row>
@@ -4709,77 +4700,77 @@
         <v>1004253</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H15" s="5" t="str">
         <f>IFERROR(MOD(14-(MATCH("OFF",I15:AL15,0)-1)-1,14)+1,"10")</f>
         <v>10</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y15" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA15" s="6" t="s">
         <v>0</v>
@@ -4824,19 +4815,19 @@
         <v>202809252</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H16" s="5">
         <f t="shared" si="1"/>
@@ -4867,7 +4858,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>0</v>
@@ -4885,28 +4876,28 @@
         <v>0</v>
       </c>
       <c r="W16" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X16" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y16" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB16" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC16" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD16" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE16" s="6" t="s">
         <v>0</v>
@@ -4927,10 +4918,10 @@
         <v>0</v>
       </c>
       <c r="AK16" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL16" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM16" s="8"/>
     </row>
@@ -4939,26 +4930,26 @@
         <v>201409252</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H17" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>0</v>
@@ -4979,28 +4970,28 @@
         <v>0</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W17" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X17" s="6" t="s">
         <v>0</v>
@@ -5024,25 +5015,25 @@
         <v>0</v>
       </c>
       <c r="AE17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK17" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL17" s="6" t="s">
         <v>0</v>
@@ -5054,19 +5045,19 @@
         <v>200811251</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" s="5">
         <f t="shared" si="1"/>
@@ -5079,22 +5070,22 @@
         <v>0</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>0</v>
@@ -5118,25 +5109,25 @@
         <v>0</v>
       </c>
       <c r="X18" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y18" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z18" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB18" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC18" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD18" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE18" s="6" t="s">
         <v>0</v>
@@ -5160,7 +5151,7 @@
         <v>0</v>
       </c>
       <c r="AL18" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="AM18" s="8"/>
     </row>
@@ -5169,104 +5160,104 @@
         <v>2804232</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H19" s="5" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y19" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ19" s="6" t="s">
         <v>0</v>
@@ -5284,92 +5275,92 @@
         <v>1510243</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H20" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y20" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF20" s="6" t="s">
         <v>0</v>
@@ -5384,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="AJ20" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK20" s="6" t="s">
         <v>0</v>
@@ -5399,77 +5390,77 @@
         <v>2106234</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D21" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H21" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y21" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA21" s="6" t="s">
         <v>0</v>
@@ -5481,28 +5472,28 @@
         <v>0</v>
       </c>
       <c r="AD21" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE21" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF21" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG21" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH21" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI21" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ21" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK21" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL21" s="6" t="s">
         <v>0</v>
@@ -5514,32 +5505,32 @@
         <v>1510241</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D22" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H22" s="5">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>0</v>
@@ -5551,76 +5542,76 @@
         <v>0</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y22" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM22" s="8"/>
     </row>
@@ -5629,77 +5620,77 @@
         <v>207251</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H23" s="5">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>0</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U23" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V23" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W23" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X23" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y23" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z23" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA23" s="6" t="s">
         <v>0</v>
@@ -5729,13 +5720,13 @@
         <v>0</v>
       </c>
       <c r="AJ23" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK23" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL23" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM23" s="8"/>
     </row>
@@ -5744,19 +5735,19 @@
         <v>1906254</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H24" s="5">
         <f t="shared" si="1"/>
@@ -5766,16 +5757,16 @@
         <v>0</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>0</v>
@@ -5793,31 +5784,31 @@
         <v>0</v>
       </c>
       <c r="S24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y24" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA24" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB24" s="6" t="s">
         <v>0</v>
@@ -5826,31 +5817,31 @@
         <v>0</v>
       </c>
       <c r="AD24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ24" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK24" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL24" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM24" s="8"/>
     </row>
@@ -5859,19 +5850,19 @@
         <v>2802252</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H25" s="5">
         <f t="shared" si="1"/>
@@ -5884,13 +5875,13 @@
         <v>0</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>0</v>
@@ -5905,67 +5896,67 @@
         <v>0</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y25" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM25" s="8"/>
     </row>
@@ -5974,110 +5965,110 @@
         <v>2802253</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H26" s="5" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y26" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL26" s="6" t="s">
         <v>0</v>
@@ -6089,19 +6080,19 @@
         <v>1402231</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D27" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H27" s="5">
         <f t="shared" si="1"/>
@@ -6120,16 +6111,16 @@
         <v>0</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q27" s="6" t="s">
         <v>0</v>
@@ -6162,16 +6153,16 @@
         <v>0</v>
       </c>
       <c r="AA27" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB27" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC27" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD27" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE27" s="6" t="s">
         <v>0</v>
@@ -6192,10 +6183,10 @@
         <v>0</v>
       </c>
       <c r="AK27" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL27" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM27" s="8"/>
     </row>
@@ -6204,110 +6195,110 @@
         <v>200509251</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D28" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H28" s="5" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y28" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL28" s="6" t="s">
         <v>0</v>
@@ -6319,113 +6310,113 @@
         <v>202809251</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D29" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H29" s="5" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y29" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM29" s="8"/>
     </row>
@@ -6434,53 +6425,53 @@
         <v>201261</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D30" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="F30" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H30" s="5">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S30" s="6" t="s">
         <v>0</v>
@@ -6504,19 +6495,19 @@
         <v>0</v>
       </c>
       <c r="Z30" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA30" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB30" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC30" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD30" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE30" s="6" t="s">
         <v>0</v>
@@ -6549,19 +6540,19 @@
         <v>2405261</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D31" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H31" s="5">
         <f t="shared" si="1"/>
@@ -6583,19 +6574,19 @@
         <v>0</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S31" s="6" t="s">
         <v>0</v>
@@ -6628,34 +6619,34 @@
         <v>0</v>
       </c>
       <c r="AC31" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD31" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE31" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF31" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG31" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH31" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI31" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ31" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK31" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL31" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM31" s="8"/>
     </row>
@@ -6664,19 +6655,19 @@
         <v>2405262</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D32" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="F32" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H32" s="5">
         <f t="shared" si="1"/>
@@ -6704,16 +6695,16 @@
         <v>0</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S32" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T32" s="6" t="s">
         <v>0</v>
@@ -6737,40 +6728,40 @@
         <v>0</v>
       </c>
       <c r="AA32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM32" s="8"/>
     </row>
@@ -6779,19 +6770,19 @@
         <v>1906252</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G33" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H33" s="5" t="str">
         <f>IFERROR(MOD(14-(MATCH("OFF",I33:AL33,0)-1)-1,14)+1,"8")</f>
@@ -6810,55 +6801,55 @@
         <v>0</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y33" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB33" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC33" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD33" s="6" t="s">
         <v>0</v>
@@ -6894,19 +6885,19 @@
         <v>201409251</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G34" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H34" s="5">
         <f t="shared" si="1"/>
@@ -6922,7 +6913,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>0</v>
@@ -6964,43 +6955,43 @@
         <v>0</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL34" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM34" s="8"/>
     </row>
@@ -7009,19 +7000,19 @@
         <v>206231</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="E35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G35" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H35" s="5">
         <f t="shared" si="1"/>
@@ -7043,7 +7034,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>0</v>
@@ -7085,7 +7076,7 @@
         <v>0</v>
       </c>
       <c r="AB35" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC35" s="6" t="s">
         <v>0</v>
@@ -7124,19 +7115,19 @@
         <v>2703251</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="E36" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F36" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G36" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H36" s="5">
         <f t="shared" si="1"/>
@@ -7179,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V36" s="6" t="s">
         <v>0</v>
@@ -7221,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ36" s="6" t="s">
         <v>0</v>
@@ -7239,19 +7230,19 @@
         <v>1303221</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="E37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G37" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H37" s="5" t="str">
         <f>IFERROR(MOD(14-(MATCH("OFF",I37:AL37,0)-1)-1,14)+1,"10")</f>
@@ -7285,55 +7276,55 @@
         <v>0</v>
       </c>
       <c r="R37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH37" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI37" s="16" t="s">
         <v>0</v>
@@ -7354,19 +7345,19 @@
         <v>108235</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="E38" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G38" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H38" s="5" t="str">
         <f>IFERROR(MOD(14-(MATCH("OFF",I38:AL38,0)-1)-1,14)+1,"9")</f>
@@ -7379,64 +7370,64 @@
         <v>0</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y38" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB38" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC38" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD38" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE38" s="6" t="s">
         <v>0</v>
@@ -7454,13 +7445,13 @@
         <v>0</v>
       </c>
       <c r="AJ38" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK38" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL38" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM38" s="8"/>
     </row>
@@ -7469,19 +7460,19 @@
         <v>108238</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="E39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G39" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H39" s="5">
         <f t="shared" si="1"/>
@@ -7518,7 +7509,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T39" s="6" t="s">
         <v>0</v>
@@ -7545,22 +7536,22 @@
         <v>0</v>
       </c>
       <c r="AB39" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC39" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD39" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE39" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF39" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG39" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH39" s="6" t="s">
         <v>0</v>
@@ -7584,19 +7575,19 @@
         <v>2910241</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="E40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G40" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H40" s="5">
         <f t="shared" si="1"/>
@@ -7606,22 +7597,22 @@
         <v>0</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>0</v>
@@ -7663,34 +7654,34 @@
         <v>0</v>
       </c>
       <c r="AC40" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD40" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE40" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF40" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG40" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH40" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI40" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ40" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK40" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL40" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM40" s="8"/>
     </row>
@@ -7699,19 +7690,19 @@
         <v>207253</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="E41" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G41" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H41" s="5">
         <f t="shared" si="1"/>
@@ -7727,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>0</v>
@@ -7754,7 +7745,7 @@
         <v>0</v>
       </c>
       <c r="U41" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V41" s="6" t="s">
         <v>0</v>
@@ -7796,7 +7787,7 @@
         <v>0</v>
       </c>
       <c r="AI41" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ41" s="6" t="s">
         <v>0</v>
@@ -7814,29 +7805,29 @@
         <v>1102261</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="E42" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G42" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H42" s="5">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>0</v>
@@ -7878,7 +7869,7 @@
         <v>0</v>
       </c>
       <c r="X42" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y42" s="7" t="s">
         <v>0</v>
@@ -7920,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="AL42" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM42" s="8"/>
     </row>
@@ -7929,19 +7920,19 @@
         <v>1507261</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="E43" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G43" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H43" s="5">
         <f t="shared" si="1"/>
@@ -7966,16 +7957,16 @@
         <v>0</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S43" s="6" t="s">
         <v>0</v>
@@ -8014,28 +8005,28 @@
         <v>0</v>
       </c>
       <c r="AE43" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF43" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG43" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH43" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI43" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ43" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK43" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL43" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM43" s="17"/>
     </row>
@@ -8044,19 +8035,19 @@
         <v>1706261</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H44" s="5">
         <f t="shared" si="1"/>
@@ -8093,7 +8084,7 @@
         <v>0</v>
       </c>
       <c r="S44" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T44" s="6" t="s">
         <v>0</v>
@@ -8135,22 +8126,22 @@
         <v>0</v>
       </c>
       <c r="AG44" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH44" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI44" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ44" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK44" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL44" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM44" s="8"/>
     </row>
@@ -8159,19 +8150,19 @@
         <v>2107261</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H45" s="5">
         <f t="shared" si="1"/>
@@ -8211,52 +8202,52 @@
         <v>0</v>
       </c>
       <c r="T45" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U45" s="6" t="s">
         <v>0</v>
       </c>
       <c r="V45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI45" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ45" s="6" t="s">
         <v>0</v>
@@ -8274,26 +8265,26 @@
         <v>2307261</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="E46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G46" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H46" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="I46" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J46" s="18" t="s">
         <v>0</v>
@@ -8320,22 +8311,22 @@
         <v>0</v>
       </c>
       <c r="R46" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S46" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T46" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U46" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V46" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W46" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X46" s="21" t="s">
         <v>0</v>
@@ -8365,13 +8356,13 @@
         <v>0</v>
       </c>
       <c r="AG46" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH46" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI46" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ46" s="21" t="s">
         <v>0</v>
@@ -8389,19 +8380,19 @@
         <v>1508264</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H47" s="5">
         <f t="shared" si="1"/>
@@ -8414,7 +8405,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L47" s="18" t="s">
         <v>0</v>
@@ -8429,19 +8420,19 @@
         <v>0</v>
       </c>
       <c r="P47" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q47" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R47" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S47" s="105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T47" s="105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U47" s="18" t="s">
         <v>0</v>
@@ -8471,19 +8462,19 @@
         <v>0</v>
       </c>
       <c r="AD47" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE47" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF47" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG47" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH47" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI47" s="21" t="s">
         <v>0</v>
@@ -8504,32 +8495,32 @@
         <v>1508261</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D48" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="F48" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="G48" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H48" s="5">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I48" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J48" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K48" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L48" s="18" t="s">
         <v>0</v>
@@ -8550,28 +8541,28 @@
         <v>0</v>
       </c>
       <c r="R48" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S48" s="105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T48" s="105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U48" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V48" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W48" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X48" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y48" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z48" s="21" t="s">
         <v>0</v>
@@ -8586,31 +8577,31 @@
         <v>0</v>
       </c>
       <c r="AD48" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE48" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF48" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG48" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH48" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI48" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ48" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK48" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL48" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM48" s="22"/>
     </row>
@@ -8619,19 +8610,19 @@
         <v>1508262</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D49" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="F49" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="G49" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H49" s="5">
         <f t="shared" si="1"/>
@@ -8644,19 +8635,19 @@
         <v>0</v>
       </c>
       <c r="K49" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L49" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M49" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N49" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O49" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P49" s="18" t="s">
         <v>0</v>
@@ -8686,19 +8677,19 @@
         <v>0</v>
       </c>
       <c r="Y49" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z49" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA49" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB49" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC49" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD49" s="21" t="s">
         <v>0</v>
@@ -8725,7 +8716,7 @@
         <v>0</v>
       </c>
       <c r="AL49" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM49" s="22"/>
     </row>
@@ -8734,19 +8725,19 @@
         <v>1508263</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D50" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="F50" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="G50" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H50" s="5">
         <f t="shared" si="1"/>
@@ -8771,76 +8762,76 @@
         <v>0</v>
       </c>
       <c r="O50" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P50" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q50" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R50" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S50" s="105" t="s">
         <v>0</v>
       </c>
       <c r="T50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF50" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG50" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH50" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI50" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ50" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK50" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL50" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM50" s="22"/>
     </row>
@@ -8882,7 +8873,7 @@
     </row>
     <row r="52" spans="2:39">
       <c r="B52" s="25" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
@@ -8920,7 +8911,7 @@
     </row>
     <row r="53" spans="2:39">
       <c r="B53" s="27" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C53" s="28"/>
       <c r="D53" s="28"/>
@@ -10274,7 +10265,7 @@
     </row>
     <row r="70" spans="2:35">
       <c r="B70" s="25" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
@@ -10312,7 +10303,7 @@
     </row>
     <row r="71" spans="2:35">
       <c r="B71" s="27" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C71" s="27"/>
       <c r="D71" s="27"/>
@@ -15750,40 +15741,40 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="B1" s="107" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C1" s="107" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D1" s="107" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E1" s="107" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="F1" s="110" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G1" s="107" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H1" s="107"/>
       <c r="I1" s="107"/>
       <c r="J1" s="106" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="K1" s="106"/>
       <c r="L1" s="106"/>
       <c r="M1" s="107" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="N1" s="107"/>
       <c r="O1" s="107"/>
       <c r="P1" s="107" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="Q1" s="108" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -15793,31 +15784,31 @@
       <c r="E2" s="107"/>
       <c r="F2" s="110"/>
       <c r="G2" s="62" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="H2" s="62" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="I2" s="62" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="J2" s="62" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="K2" s="62" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="L2" s="62" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="M2" s="62" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="N2" s="62" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="O2" s="62" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="P2" s="107"/>
       <c r="Q2" s="109"/>
@@ -15834,7 +15825,7 @@
         <v>207231</v>
       </c>
       <c r="D3" s="104" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E3" s="67">
         <v>46268</v>
@@ -15859,7 +15850,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="Q3" s="73" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="63" customFormat="1" ht="16">
@@ -15874,7 +15865,7 @@
         <v>207231</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E4" s="67">
         <v>46270</v>
@@ -15899,7 +15890,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="Q4" s="73" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="63" customFormat="1" ht="16">
@@ -15914,7 +15905,7 @@
         <v>207231</v>
       </c>
       <c r="D5" s="66" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E5" s="67">
         <v>46273</v>
@@ -15939,7 +15930,7 @@
         <v>2.1527777777777778E-2</v>
       </c>
       <c r="Q5" s="73" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="63" customFormat="1" ht="16">
@@ -15954,7 +15945,7 @@
         <v>207231</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E6" s="67">
         <v>46274</v>
@@ -15979,7 +15970,7 @@
         <v>5.2083333333333336E-2</v>
       </c>
       <c r="Q6" s="73" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="63" customFormat="1" ht="16">
@@ -15994,7 +15985,7 @@
         <v>207231</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E7" s="67">
         <v>46275</v>
@@ -16019,7 +16010,7 @@
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="Q7" s="73" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="63" customFormat="1" ht="16">
@@ -16034,7 +16025,7 @@
         <v>207231</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E8" s="67">
         <v>46277</v>
@@ -16059,7 +16050,7 @@
         <v>6.25E-2</v>
       </c>
       <c r="Q8" s="73" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="63" customFormat="1" ht="16">
@@ -16074,7 +16065,7 @@
         <v>201261</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E9" s="67">
         <v>46276</v>
@@ -16099,7 +16090,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="Q9" s="73" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="63" customFormat="1" ht="16">
@@ -16114,7 +16105,7 @@
         <v>207231</v>
       </c>
       <c r="D10" s="104" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E10" s="67">
         <v>46281</v>
@@ -16139,7 +16130,7 @@
         <v>6.25E-2</v>
       </c>
       <c r="Q10" s="73" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="63" customFormat="1" ht="16">
@@ -16154,7 +16145,7 @@
         <v>207253</v>
       </c>
       <c r="D11" s="66" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E11" s="67">
         <v>46283</v>
@@ -16179,7 +16170,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="Q11" s="73" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="63" customFormat="1" ht="16">

--- a/1_Data_Master/Data Absensi_BMP.xlsx
+++ b/1_Data_Master/Data Absensi_BMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GENERAL PSD\PENDINGAN LINDAA 2026\GENERAL 2026\00. PORTAL TIMESHEET\1_Data_Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C81FC8-3603-4A84-869A-EF8AD25A25C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8755AFA0-72A9-4351-8673-ABA1F8973DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CEF79333-F3A4-451D-BE26-4BA9C1711C1C}"/>
   </bookViews>
@@ -1322,12 +1322,6 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1347,6 +1341,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2899,7 +2899,8 @@
     <col min="6" max="6" width="48.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.453125" style="1" customWidth="1"/>
-    <col min="9" max="38" width="5.7265625" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="38" width="11.54296875" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="20.453125" customWidth="1"/>
     <col min="40" max="40" width="24.90625" customWidth="1"/>
     <col min="41" max="41" width="33.54296875" customWidth="1"/>
@@ -2930,123 +2931,124 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="97">
-        <v>1</v>
-      </c>
-      <c r="J1" s="97">
+      <c r="I1" s="104">
+        <v>46266</v>
+      </c>
+      <c r="J1" s="104">
         <f>I1+1</f>
-        <v>2</v>
-      </c>
-      <c r="K1" s="97">
+        <v>46267</v>
+      </c>
+      <c r="K1" s="104">
         <f t="shared" ref="K1:AK1" si="0">J1+1</f>
-        <v>3</v>
-      </c>
-      <c r="L1" s="97">
+        <v>46268</v>
+      </c>
+      <c r="L1" s="104">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="M1" s="97">
+        <v>46269</v>
+      </c>
+      <c r="M1" s="104">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N1" s="97">
+        <v>46270</v>
+      </c>
+      <c r="N1" s="104">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="O1" s="97">
+        <v>46271</v>
+      </c>
+      <c r="O1" s="104">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="P1" s="97">
+        <v>46272</v>
+      </c>
+      <c r="P1" s="104">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="Q1" s="97">
+        <v>46273</v>
+      </c>
+      <c r="Q1" s="104">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="R1" s="97">
+        <v>46274</v>
+      </c>
+      <c r="R1" s="104">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="S1" s="97">
+        <v>46275</v>
+      </c>
+      <c r="S1" s="104">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="T1" s="97">
+        <v>46276</v>
+      </c>
+      <c r="T1" s="104">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="U1" s="97">
+        <v>46277</v>
+      </c>
+      <c r="U1" s="104">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="V1" s="97">
+        <v>46278</v>
+      </c>
+      <c r="V1" s="104">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="W1" s="97">
+        <v>46279</v>
+      </c>
+      <c r="W1" s="104">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="X1" s="97">
+        <v>46280</v>
+      </c>
+      <c r="X1" s="104">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="Y1" s="98">
+        <v>46281</v>
+      </c>
+      <c r="Y1" s="105">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="Z1" s="97">
+        <v>46282</v>
+      </c>
+      <c r="Z1" s="104">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="AA1" s="97">
+        <v>46283</v>
+      </c>
+      <c r="AA1" s="104">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AB1" s="97">
+        <v>46284</v>
+      </c>
+      <c r="AB1" s="104">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AC1" s="97">
+        <v>46285</v>
+      </c>
+      <c r="AC1" s="104">
         <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AD1" s="97">
+        <v>46286</v>
+      </c>
+      <c r="AD1" s="104">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="AE1" s="97">
+        <v>46287</v>
+      </c>
+      <c r="AE1" s="104">
         <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="AF1" s="97">
+        <v>46288</v>
+      </c>
+      <c r="AF1" s="104">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AG1" s="97">
+        <v>46289</v>
+      </c>
+      <c r="AG1" s="104">
         <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AH1" s="97">
+        <v>46290</v>
+      </c>
+      <c r="AH1" s="104">
         <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AI1" s="97">
+        <v>46291</v>
+      </c>
+      <c r="AI1" s="104">
         <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="AJ1" s="97">
+        <v>46292</v>
+      </c>
+      <c r="AJ1" s="104">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="AK1" s="97">
+        <v>46293</v>
+      </c>
+      <c r="AK1" s="104">
         <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="AL1" s="97">
-        <v>30</v>
+        <v>46294</v>
+      </c>
+      <c r="AL1" s="104">
+        <f>AK1+1</f>
+        <v>46295</v>
       </c>
       <c r="AO1" s="3" t="s">
         <v>4</v>
@@ -8428,10 +8430,10 @@
       <c r="R47" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="S47" s="105" t="s">
-        <v>22</v>
-      </c>
-      <c r="T47" s="105" t="s">
+      <c r="S47" s="103" t="s">
+        <v>22</v>
+      </c>
+      <c r="T47" s="103" t="s">
         <v>15</v>
       </c>
       <c r="U47" s="18" t="s">
@@ -8543,10 +8545,10 @@
       <c r="R48" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="S48" s="105" t="s">
-        <v>22</v>
-      </c>
-      <c r="T48" s="105" t="s">
+      <c r="S48" s="103" t="s">
+        <v>22</v>
+      </c>
+      <c r="T48" s="103" t="s">
         <v>22</v>
       </c>
       <c r="U48" s="18" t="s">
@@ -8658,10 +8660,10 @@
       <c r="R49" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="S49" s="105" t="s">
-        <v>0</v>
-      </c>
-      <c r="T49" s="105" t="s">
+      <c r="S49" s="103" t="s">
+        <v>0</v>
+      </c>
+      <c r="T49" s="103" t="s">
         <v>0</v>
       </c>
       <c r="U49" s="18" t="s">
@@ -8773,7 +8775,7 @@
       <c r="R50" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="S50" s="105" t="s">
+      <c r="S50" s="103" t="s">
         <v>0</v>
       </c>
       <c r="T50" s="7" t="s">
@@ -15824,7 +15826,7 @@
       <c r="C3" s="65">
         <v>207231</v>
       </c>
-      <c r="D3" s="104" t="s">
+      <c r="D3" s="102" t="s">
         <v>98</v>
       </c>
       <c r="E3" s="67">
@@ -16104,7 +16106,7 @@
       <c r="C10" s="65">
         <v>207231</v>
       </c>
-      <c r="D10" s="104" t="s">
+      <c r="D10" s="102" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="67">
@@ -16182,8 +16184,8 @@
         <v>13</v>
       </c>
       <c r="C12" s="65"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="103"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="101"/>
       <c r="F12" s="64"/>
       <c r="G12" s="68"/>
       <c r="H12" s="69"/>
@@ -16191,9 +16193,9 @@
       <c r="J12" s="64"/>
       <c r="K12" s="64"/>
       <c r="L12" s="71"/>
-      <c r="M12" s="100"/>
-      <c r="N12" s="100"/>
-      <c r="O12" s="101"/>
+      <c r="M12" s="98"/>
+      <c r="N12" s="98"/>
+      <c r="O12" s="99"/>
       <c r="P12" s="72"/>
       <c r="Q12" s="73"/>
     </row>
@@ -16206,8 +16208,8 @@
         <v>14</v>
       </c>
       <c r="C13" s="65"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="103"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="101"/>
       <c r="F13" s="64"/>
       <c r="G13" s="68"/>
       <c r="H13" s="69"/>
@@ -16215,9 +16217,9 @@
       <c r="J13" s="64"/>
       <c r="K13" s="64"/>
       <c r="L13" s="71"/>
-      <c r="M13" s="100"/>
-      <c r="N13" s="100"/>
-      <c r="O13" s="101"/>
+      <c r="M13" s="98"/>
+      <c r="N13" s="98"/>
+      <c r="O13" s="99"/>
       <c r="P13" s="72"/>
       <c r="Q13" s="73"/>
     </row>
@@ -16230,8 +16232,8 @@
         <v>15</v>
       </c>
       <c r="C14" s="65"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="103"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="101"/>
       <c r="F14" s="64"/>
       <c r="G14" s="68"/>
       <c r="H14" s="69"/>
@@ -16239,9 +16241,9 @@
       <c r="J14" s="64"/>
       <c r="K14" s="64"/>
       <c r="L14" s="71"/>
-      <c r="M14" s="100"/>
-      <c r="N14" s="100"/>
-      <c r="O14" s="101"/>
+      <c r="M14" s="98"/>
+      <c r="N14" s="98"/>
+      <c r="O14" s="99"/>
       <c r="P14" s="72"/>
       <c r="Q14" s="73"/>
     </row>
@@ -16254,8 +16256,8 @@
         <v>16</v>
       </c>
       <c r="C15" s="65"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="103"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="101"/>
       <c r="F15" s="64"/>
       <c r="G15" s="68"/>
       <c r="H15" s="69"/>
@@ -16263,9 +16265,9 @@
       <c r="J15" s="64"/>
       <c r="K15" s="64"/>
       <c r="L15" s="71"/>
-      <c r="M15" s="100"/>
-      <c r="N15" s="100"/>
-      <c r="O15" s="101"/>
+      <c r="M15" s="98"/>
+      <c r="N15" s="98"/>
+      <c r="O15" s="99"/>
       <c r="P15" s="72"/>
       <c r="Q15" s="73"/>
     </row>
@@ -16279,7 +16281,7 @@
       </c>
       <c r="C16" s="65"/>
       <c r="D16" s="66"/>
-      <c r="E16" s="103"/>
+      <c r="E16" s="101"/>
       <c r="F16" s="64"/>
       <c r="G16" s="68"/>
       <c r="H16" s="69"/>
@@ -16287,9 +16289,9 @@
       <c r="J16" s="64"/>
       <c r="K16" s="64"/>
       <c r="L16" s="71"/>
-      <c r="M16" s="100"/>
-      <c r="N16" s="100"/>
-      <c r="O16" s="101"/>
+      <c r="M16" s="98"/>
+      <c r="N16" s="98"/>
+      <c r="O16" s="99"/>
       <c r="P16" s="72"/>
       <c r="Q16" s="73"/>
     </row>
@@ -16302,8 +16304,8 @@
         <v>18</v>
       </c>
       <c r="C17" s="65"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="103"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="101"/>
       <c r="F17" s="64"/>
       <c r="G17" s="68"/>
       <c r="H17" s="69"/>
@@ -16311,9 +16313,9 @@
       <c r="J17" s="64"/>
       <c r="K17" s="64"/>
       <c r="L17" s="71"/>
-      <c r="M17" s="100"/>
-      <c r="N17" s="100"/>
-      <c r="O17" s="101"/>
+      <c r="M17" s="98"/>
+      <c r="N17" s="98"/>
+      <c r="O17" s="99"/>
       <c r="P17" s="72"/>
       <c r="Q17" s="73"/>
     </row>
@@ -16326,8 +16328,8 @@
         <v>19</v>
       </c>
       <c r="C18" s="65"/>
-      <c r="D18" s="99"/>
-      <c r="E18" s="103"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="101"/>
       <c r="F18" s="64"/>
       <c r="G18" s="68"/>
       <c r="H18" s="69"/>
@@ -16335,9 +16337,9 @@
       <c r="J18" s="64"/>
       <c r="K18" s="64"/>
       <c r="L18" s="71"/>
-      <c r="M18" s="100"/>
-      <c r="N18" s="100"/>
-      <c r="O18" s="101"/>
+      <c r="M18" s="98"/>
+      <c r="N18" s="98"/>
+      <c r="O18" s="99"/>
       <c r="P18" s="72"/>
       <c r="Q18" s="73"/>
     </row>
@@ -16350,8 +16352,8 @@
         <v>20</v>
       </c>
       <c r="C19" s="65"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="103"/>
+      <c r="D19" s="97"/>
+      <c r="E19" s="101"/>
       <c r="F19" s="64"/>
       <c r="G19" s="68"/>
       <c r="H19" s="69"/>
@@ -16359,9 +16361,9 @@
       <c r="J19" s="64"/>
       <c r="K19" s="64"/>
       <c r="L19" s="71"/>
-      <c r="M19" s="100"/>
-      <c r="N19" s="100"/>
-      <c r="O19" s="102"/>
+      <c r="M19" s="98"/>
+      <c r="N19" s="98"/>
+      <c r="O19" s="100"/>
       <c r="P19" s="75"/>
       <c r="Q19" s="76"/>
     </row>
@@ -16374,8 +16376,8 @@
         <v>21</v>
       </c>
       <c r="C20" s="65"/>
-      <c r="D20" s="99"/>
-      <c r="E20" s="103"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="101"/>
       <c r="F20" s="64"/>
       <c r="G20" s="68"/>
       <c r="H20" s="69"/>
@@ -16383,9 +16385,9 @@
       <c r="J20" s="64"/>
       <c r="K20" s="64"/>
       <c r="L20" s="71"/>
-      <c r="M20" s="100"/>
-      <c r="N20" s="100"/>
-      <c r="O20" s="102"/>
+      <c r="M20" s="98"/>
+      <c r="N20" s="98"/>
+      <c r="O20" s="100"/>
       <c r="P20" s="75"/>
       <c r="Q20" s="76"/>
     </row>
@@ -16398,8 +16400,8 @@
         <v>24</v>
       </c>
       <c r="C21" s="65"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="103"/>
+      <c r="D21" s="97"/>
+      <c r="E21" s="101"/>
       <c r="F21" s="64"/>
       <c r="G21" s="68"/>
       <c r="H21" s="69"/>
@@ -16407,9 +16409,9 @@
       <c r="J21" s="64"/>
       <c r="K21" s="64"/>
       <c r="L21" s="71"/>
-      <c r="M21" s="100"/>
-      <c r="N21" s="100"/>
-      <c r="O21" s="102"/>
+      <c r="M21" s="98"/>
+      <c r="N21" s="98"/>
+      <c r="O21" s="100"/>
       <c r="P21" s="75"/>
       <c r="Q21" s="76"/>
     </row>
@@ -16423,7 +16425,7 @@
       </c>
       <c r="C22" s="65"/>
       <c r="D22" s="66"/>
-      <c r="E22" s="103"/>
+      <c r="E22" s="101"/>
       <c r="F22" s="64"/>
       <c r="G22" s="68"/>
       <c r="H22" s="69"/>
@@ -16431,9 +16433,9 @@
       <c r="J22" s="64"/>
       <c r="K22" s="64"/>
       <c r="L22" s="71"/>
-      <c r="M22" s="100"/>
-      <c r="N22" s="100"/>
-      <c r="O22" s="102"/>
+      <c r="M22" s="98"/>
+      <c r="N22" s="98"/>
+      <c r="O22" s="100"/>
       <c r="P22" s="75"/>
       <c r="Q22" s="76"/>
     </row>
@@ -16447,7 +16449,7 @@
       </c>
       <c r="C23" s="65"/>
       <c r="D23" s="66"/>
-      <c r="E23" s="103"/>
+      <c r="E23" s="101"/>
       <c r="F23" s="64"/>
       <c r="G23" s="68"/>
       <c r="H23" s="69"/>
@@ -16455,9 +16457,9 @@
       <c r="J23" s="64"/>
       <c r="K23" s="64"/>
       <c r="L23" s="71"/>
-      <c r="M23" s="100"/>
-      <c r="N23" s="100"/>
-      <c r="O23" s="102"/>
+      <c r="M23" s="98"/>
+      <c r="N23" s="98"/>
+      <c r="O23" s="100"/>
       <c r="P23" s="75"/>
       <c r="Q23" s="73"/>
     </row>
@@ -16470,8 +16472,8 @@
         <v>27</v>
       </c>
       <c r="C24" s="65"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="103"/>
+      <c r="D24" s="97"/>
+      <c r="E24" s="101"/>
       <c r="F24" s="64"/>
       <c r="G24" s="68"/>
       <c r="H24" s="69"/>
@@ -16479,9 +16481,9 @@
       <c r="J24" s="64"/>
       <c r="K24" s="64"/>
       <c r="L24" s="71"/>
-      <c r="M24" s="100"/>
-      <c r="N24" s="100"/>
-      <c r="O24" s="101"/>
+      <c r="M24" s="98"/>
+      <c r="N24" s="98"/>
+      <c r="O24" s="99"/>
       <c r="P24" s="72"/>
       <c r="Q24" s="73"/>
     </row>
